--- a/IEEE TIM data/HUMAN LAB VALIDATION/Results/Reconciled_Detection_Metrics_Summary.xlsx
+++ b/IEEE TIM data/HUMAN LAB VALIDATION/Results/Reconciled_Detection_Metrics_Summary.xlsx
@@ -955,7 +955,7 @@
         <v>3.64</v>
       </c>
       <c r="P6">
-        <v>2.691</v>
+        <v>2.84</v>
       </c>
       <c r="Q6">
         <v>29</v>
@@ -1513,7 +1513,7 @@
         <v>1.636</v>
       </c>
       <c r="P15">
-        <v>1.299</v>
+        <v>1.323</v>
       </c>
       <c r="Q15">
         <v>54</v>
@@ -1947,7 +1947,7 @@
         <v>2.66</v>
       </c>
       <c r="P22">
-        <v>2.419</v>
+        <v>2.475</v>
       </c>
       <c r="Q22">
         <v>44</v>
@@ -2009,7 +2009,7 @@
         <v>4.833</v>
       </c>
       <c r="P23">
-        <v>2.793</v>
+        <v>3.802</v>
       </c>
       <c r="Q23">
         <v>36</v>
